--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291969</v>
+        <v>122291940</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>97113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337921</v>
+        <v>337875</v>
       </c>
       <c r="R2" t="n">
-        <v>6396860</v>
+        <v>6396914</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291874</v>
+        <v>122291969</v>
       </c>
       <c r="B3" t="n">
-        <v>56264</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +802,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337962</v>
+        <v>337921</v>
       </c>
       <c r="R3" t="n">
-        <v>6396934</v>
+        <v>6396860</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -900,7 +904,7 @@
         <v>122293399</v>
       </c>
       <c r="B4" t="n">
-        <v>57742</v>
+        <v>57744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,7 +1019,7 @@
         <v>122293816</v>
       </c>
       <c r="B5" t="n">
-        <v>57914</v>
+        <v>57916</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291940</v>
+        <v>122291874</v>
       </c>
       <c r="B6" t="n">
-        <v>97111</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,50 +1143,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337875</v>
+        <v>337962</v>
       </c>
       <c r="R6" t="n">
-        <v>6396914</v>
+        <v>6396934</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291940</v>
+        <v>122293816</v>
       </c>
       <c r="B2" t="n">
-        <v>97113</v>
+        <v>57916</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337875</v>
+        <v>337799</v>
       </c>
       <c r="R2" t="n">
-        <v>6396914</v>
+        <v>6396896</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291969</v>
+        <v>122291940</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>97113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337921</v>
+        <v>337875</v>
       </c>
       <c r="R3" t="n">
-        <v>6396860</v>
+        <v>6396914</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293399</v>
+        <v>122291874</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>56266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,50 +917,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337904</v>
+        <v>337962</v>
       </c>
       <c r="R4" t="n">
-        <v>6396902</v>
+        <v>6396934</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293816</v>
+        <v>122293399</v>
       </c>
       <c r="B5" t="n">
-        <v>57916</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337799</v>
+        <v>337904</v>
       </c>
       <c r="R5" t="n">
-        <v>6396896</v>
+        <v>6396902</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291874</v>
+        <v>122291969</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,46 +1143,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337962</v>
+        <v>337921</v>
       </c>
       <c r="R6" t="n">
-        <v>6396934</v>
+        <v>6396860</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293816</v>
+        <v>122291969</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337799</v>
+        <v>337921</v>
       </c>
       <c r="R2" t="n">
-        <v>6396896</v>
+        <v>6396860</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293399</v>
+        <v>122291874</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>56266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,50 +798,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337904</v>
+        <v>337962</v>
       </c>
       <c r="R3" t="n">
-        <v>6396902</v>
+        <v>6396934</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291969</v>
+        <v>122293816</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>57916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,10 +930,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337921</v>
+        <v>337799</v>
       </c>
       <c r="R4" t="n">
-        <v>6396860</v>
+        <v>6396896</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291874</v>
+        <v>122293399</v>
       </c>
       <c r="B5" t="n">
-        <v>56266</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1024,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337962</v>
+        <v>337904</v>
       </c>
       <c r="R5" t="n">
-        <v>6396934</v>
+        <v>6396902</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293816</v>
+        <v>122293399</v>
       </c>
       <c r="B4" t="n">
-        <v>57916</v>
+        <v>57744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337799</v>
+        <v>337904</v>
       </c>
       <c r="R4" t="n">
-        <v>6396896</v>
+        <v>6396902</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293399</v>
+        <v>122291940</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>97129</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1028,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337904</v>
+        <v>337875</v>
       </c>
       <c r="R5" t="n">
-        <v>6396902</v>
+        <v>6396914</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291940</v>
+        <v>122293816</v>
       </c>
       <c r="B6" t="n">
-        <v>97129</v>
+        <v>57916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,31 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337875</v>
+        <v>337799</v>
       </c>
       <c r="R6" t="n">
-        <v>6396914</v>
+        <v>6396896</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291969</v>
+        <v>122291940</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337921</v>
+        <v>337875</v>
       </c>
       <c r="R2" t="n">
-        <v>6396860</v>
+        <v>6396914</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291874</v>
+        <v>122291969</v>
       </c>
       <c r="B3" t="n">
-        <v>56266</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +802,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337962</v>
+        <v>337921</v>
       </c>
       <c r="R3" t="n">
-        <v>6396934</v>
+        <v>6396860</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291940</v>
+        <v>122291874</v>
       </c>
       <c r="B5" t="n">
-        <v>97129</v>
+        <v>56266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,50 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337875</v>
+        <v>337962</v>
       </c>
       <c r="R5" t="n">
-        <v>6396914</v>
+        <v>6396934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291940</v>
+        <v>122291969</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337875</v>
+        <v>337921</v>
       </c>
       <c r="R2" t="n">
-        <v>6396914</v>
+        <v>6396860</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291969</v>
+        <v>122293399</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>57744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,10 +819,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337921</v>
+        <v>337904</v>
       </c>
       <c r="R3" t="n">
-        <v>6396860</v>
+        <v>6396902</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293399</v>
+        <v>122291874</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>56266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,50 +913,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337904</v>
+        <v>337962</v>
       </c>
       <c r="R4" t="n">
-        <v>6396902</v>
+        <v>6396934</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291874</v>
+        <v>122291940</v>
       </c>
       <c r="B5" t="n">
-        <v>56266</v>
+        <v>97139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1024,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>aktiv</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337962</v>
+        <v>337875</v>
       </c>
       <c r="R5" t="n">
-        <v>6396934</v>
+        <v>6396914</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293399</v>
+        <v>122291940</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>97151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337904</v>
+        <v>337875</v>
       </c>
       <c r="R3" t="n">
-        <v>6396902</v>
+        <v>6396914</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291874</v>
+        <v>122293816</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
+        <v>57921</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +913,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337962</v>
+        <v>337799</v>
       </c>
       <c r="R4" t="n">
-        <v>6396934</v>
+        <v>6396896</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291940</v>
+        <v>122291874</v>
       </c>
       <c r="B5" t="n">
-        <v>97139</v>
+        <v>56271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,50 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337875</v>
+        <v>337962</v>
       </c>
       <c r="R5" t="n">
-        <v>6396914</v>
+        <v>6396934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293816</v>
+        <v>122293399</v>
       </c>
       <c r="B6" t="n">
-        <v>57916</v>
+        <v>57749</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,16 +1143,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337799</v>
+        <v>337904</v>
       </c>
       <c r="R6" t="n">
-        <v>6396896</v>
+        <v>6396902</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291940</v>
+        <v>122291874</v>
       </c>
       <c r="B3" t="n">
-        <v>97151</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +798,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337875</v>
+        <v>337962</v>
       </c>
       <c r="R3" t="n">
-        <v>6396914</v>
+        <v>6396934</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293816</v>
+        <v>122291940</v>
       </c>
       <c r="B4" t="n">
-        <v>57921</v>
+        <v>97156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337799</v>
+        <v>337875</v>
       </c>
       <c r="R4" t="n">
-        <v>6396896</v>
+        <v>6396914</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291874</v>
+        <v>122293816</v>
       </c>
       <c r="B5" t="n">
-        <v>56271</v>
+        <v>57921</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1024,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337962</v>
+        <v>337799</v>
       </c>
       <c r="R5" t="n">
-        <v>6396934</v>
+        <v>6396896</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291969</v>
+        <v>122291874</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>56271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337921</v>
+        <v>337962</v>
       </c>
       <c r="R2" t="n">
-        <v>6396860</v>
+        <v>6396934</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291874</v>
+        <v>122293816</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>57921</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +793,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>102990</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337962</v>
+        <v>337799</v>
       </c>
       <c r="R3" t="n">
-        <v>6396934</v>
+        <v>6396896</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291940</v>
+        <v>122293399</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>57749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337875</v>
+        <v>337904</v>
       </c>
       <c r="R4" t="n">
-        <v>6396914</v>
+        <v>6396902</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293816</v>
+        <v>122291940</v>
       </c>
       <c r="B5" t="n">
-        <v>57921</v>
+        <v>97165</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337799</v>
+        <v>337875</v>
       </c>
       <c r="R5" t="n">
-        <v>6396896</v>
+        <v>6396914</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,12 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1100,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1127,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293399</v>
+        <v>122291969</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,16 +1127,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1160,14 +1139,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337904</v>
+        <v>337921</v>
       </c>
       <c r="R6" t="n">
-        <v>6396902</v>
+        <v>6396860</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291874</v>
+        <v>122293816</v>
       </c>
       <c r="B2" t="n">
-        <v>56271</v>
+        <v>57925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>102990</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337962</v>
+        <v>337799</v>
       </c>
       <c r="R2" t="n">
-        <v>6396934</v>
+        <v>6396896</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293816</v>
+        <v>122291969</v>
       </c>
       <c r="B3" t="n">
-        <v>57921</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,11 +806,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>105930</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -809,14 +823,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337799</v>
+        <v>337921</v>
       </c>
       <c r="R3" t="n">
-        <v>6396896</v>
+        <v>6396860</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -891,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293399</v>
+        <v>122291940</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>97178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +917,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -935,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337904</v>
+        <v>337875</v>
       </c>
       <c r="R4" t="n">
-        <v>6396902</v>
+        <v>6396914</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291940</v>
+        <v>122293399</v>
       </c>
       <c r="B5" t="n">
-        <v>97165</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,26 +1032,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337875</v>
+        <v>337904</v>
       </c>
       <c r="R5" t="n">
-        <v>6396914</v>
+        <v>6396902</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1111,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291969</v>
+        <v>122291874</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>56275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,41 +1143,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337921</v>
+        <v>337962</v>
       </c>
       <c r="R6" t="n">
-        <v>6396860</v>
+        <v>6396934</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293816</v>
+        <v>122291874</v>
       </c>
       <c r="B2" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337799</v>
+        <v>337962</v>
       </c>
       <c r="R2" t="n">
-        <v>6396896</v>
+        <v>6396934</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291969</v>
+        <v>122293399</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,10 +819,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337921</v>
+        <v>337904</v>
       </c>
       <c r="R3" t="n">
-        <v>6396860</v>
+        <v>6396902</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -904,7 +904,7 @@
         <v>122291940</v>
       </c>
       <c r="B4" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293399</v>
+        <v>122291969</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,14 +1049,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337904</v>
+        <v>337921</v>
       </c>
       <c r="R5" t="n">
-        <v>6396902</v>
+        <v>6396860</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291874</v>
+        <v>122293816</v>
       </c>
       <c r="B6" t="n">
-        <v>56275</v>
+        <v>57925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,46 +1139,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337962</v>
+        <v>337799</v>
       </c>
       <c r="R6" t="n">
-        <v>6396934</v>
+        <v>6396896</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291874</v>
+        <v>122291969</v>
       </c>
       <c r="B2" t="n">
-        <v>56275</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337962</v>
+        <v>337921</v>
       </c>
       <c r="R2" t="n">
-        <v>6396934</v>
+        <v>6396860</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293399</v>
+        <v>122291874</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>56275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +798,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337904</v>
+        <v>337962</v>
       </c>
       <c r="R3" t="n">
-        <v>6396902</v>
+        <v>6396934</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291969</v>
+        <v>122293816</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>57925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1028,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,10 +1045,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337921</v>
+        <v>337799</v>
       </c>
       <c r="R5" t="n">
-        <v>6396860</v>
+        <v>6396896</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293816</v>
+        <v>122293399</v>
       </c>
       <c r="B6" t="n">
-        <v>57925</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,16 +1143,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337799</v>
+        <v>337904</v>
       </c>
       <c r="R6" t="n">
-        <v>6396896</v>
+        <v>6396902</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291969</v>
+        <v>122293816</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>57925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337921</v>
+        <v>337799</v>
       </c>
       <c r="R2" t="n">
-        <v>6396860</v>
+        <v>6396896</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291874</v>
+        <v>122291969</v>
       </c>
       <c r="B3" t="n">
-        <v>56275</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +802,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337962</v>
+        <v>337921</v>
       </c>
       <c r="R3" t="n">
-        <v>6396934</v>
+        <v>6396860</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -900,7 +904,7 @@
         <v>122291940</v>
       </c>
       <c r="B4" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293816</v>
+        <v>122291874</v>
       </c>
       <c r="B5" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,50 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337799</v>
+        <v>337962</v>
       </c>
       <c r="R5" t="n">
-        <v>6396896</v>
+        <v>6396934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293816</v>
+        <v>122293399</v>
       </c>
       <c r="B2" t="n">
-        <v>57925</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337799</v>
+        <v>337904</v>
       </c>
       <c r="R2" t="n">
-        <v>6396896</v>
+        <v>6396902</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291969</v>
+        <v>122291940</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>97194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337921</v>
+        <v>337875</v>
       </c>
       <c r="R3" t="n">
-        <v>6396860</v>
+        <v>6396914</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291940</v>
+        <v>122293816</v>
       </c>
       <c r="B4" t="n">
-        <v>97194</v>
+        <v>57925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337875</v>
+        <v>337799</v>
       </c>
       <c r="R4" t="n">
-        <v>6396914</v>
+        <v>6396896</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1127,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293399</v>
+        <v>122291969</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,16 +1147,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1160,14 +1164,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337904</v>
+        <v>337921</v>
       </c>
       <c r="R6" t="n">
-        <v>6396902</v>
+        <v>6396860</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293399</v>
+        <v>122291874</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>56276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337904</v>
+        <v>337962</v>
       </c>
       <c r="R2" t="n">
-        <v>6396902</v>
+        <v>6396934</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291940</v>
+        <v>122293816</v>
       </c>
       <c r="B3" t="n">
-        <v>97194</v>
+        <v>57926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337875</v>
+        <v>337799</v>
       </c>
       <c r="R3" t="n">
-        <v>6396914</v>
+        <v>6396896</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293816</v>
+        <v>122291969</v>
       </c>
       <c r="B4" t="n">
-        <v>57925</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,14 +934,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337799</v>
+        <v>337921</v>
       </c>
       <c r="R4" t="n">
-        <v>6396896</v>
+        <v>6396860</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1020,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291874</v>
+        <v>122291940</v>
       </c>
       <c r="B5" t="n">
-        <v>56275</v>
+        <v>97195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,46 +1024,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>aktiv</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337962</v>
+        <v>337875</v>
       </c>
       <c r="R5" t="n">
-        <v>6396934</v>
+        <v>6396914</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291969</v>
+        <v>122293399</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,16 +1143,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,10 +1160,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337921</v>
+        <v>337904</v>
       </c>
       <c r="R6" t="n">
-        <v>6396860</v>
+        <v>6396902</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291874</v>
+        <v>122291940</v>
       </c>
       <c r="B2" t="n">
-        <v>56276</v>
+        <v>97198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>aktiv</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337962</v>
+        <v>337875</v>
       </c>
       <c r="R2" t="n">
-        <v>6396934</v>
+        <v>6396914</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291969</v>
+        <v>122291874</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>56276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +917,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337921</v>
+        <v>337962</v>
       </c>
       <c r="R4" t="n">
-        <v>6396860</v>
+        <v>6396934</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291940</v>
+        <v>122291969</v>
       </c>
       <c r="B5" t="n">
-        <v>97195</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1032,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337875</v>
+        <v>337921</v>
       </c>
       <c r="R5" t="n">
-        <v>6396914</v>
+        <v>6396860</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 3642-2021 artfynd.xlsx
+++ b/artfynd/A 3642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291940</v>
+        <v>122291874</v>
       </c>
       <c r="B2" t="n">
-        <v>97198</v>
+        <v>56276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337875</v>
+        <v>337962</v>
       </c>
       <c r="R2" t="n">
-        <v>6396914</v>
+        <v>6396934</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293816</v>
+        <v>122293399</v>
       </c>
       <c r="B3" t="n">
-        <v>57926</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337799</v>
+        <v>337904</v>
       </c>
       <c r="R3" t="n">
-        <v>6396896</v>
+        <v>6396902</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291874</v>
+        <v>122293816</v>
       </c>
       <c r="B4" t="n">
-        <v>56276</v>
+        <v>57926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,46 +913,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337962</v>
+        <v>337799</v>
       </c>
       <c r="R4" t="n">
-        <v>6396934</v>
+        <v>6396896</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293399</v>
+        <v>122291940</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>97198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,31 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337904</v>
+        <v>337875</v>
       </c>
       <c r="R6" t="n">
-        <v>6396902</v>
+        <v>6396914</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
